--- a/output/Data and Chart Outputs/canada_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/canada_power_capacity.xlsx
@@ -944,7 +944,7 @@
         <v>8.3725</v>
       </c>
       <c r="I2" t="n">
-        <v>32.806</v>
+        <v>18.303</v>
       </c>
     </row>
     <row r="3">
@@ -973,7 +973,7 @@
         <v>4.4845</v>
       </c>
       <c r="I3" t="n">
-        <v>32.7265</v>
+        <v>18.2235</v>
       </c>
     </row>
     <row r="4">
@@ -1002,7 +1002,7 @@
         <v>4.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>30.3495</v>
+        <v>17.0535</v>
       </c>
     </row>
     <row r="5">
@@ -1031,7 +1031,7 @@
         <v>3.2155</v>
       </c>
       <c r="I5" t="n">
-        <v>31.9452</v>
+        <v>17.7602</v>
       </c>
     </row>
   </sheetData>
@@ -1127,7 +1127,7 @@
         <v>5947.3</v>
       </c>
       <c r="I2" t="n">
-        <v>17846.9</v>
+        <v>3745.9</v>
       </c>
       <c r="J2" t="n">
         <v>145537.8</v>
@@ -1159,7 +1159,7 @@
         <v>5947.7</v>
       </c>
       <c r="I3" t="n">
-        <v>17918.4</v>
+        <v>3817.4</v>
       </c>
       <c r="J3" t="n">
         <v>145960.9</v>
@@ -1191,7 +1191,7 @@
         <v>5930.3</v>
       </c>
       <c r="I4" t="n">
-        <v>18303</v>
+        <v>3800</v>
       </c>
       <c r="J4" t="n">
         <v>149530.5</v>
@@ -1223,7 +1223,7 @@
         <v>5773.4</v>
       </c>
       <c r="I5" t="n">
-        <v>18223.5</v>
+        <v>3720.5</v>
       </c>
       <c r="J5" t="n">
         <v>151706.7</v>
@@ -1255,7 +1255,7 @@
         <v>5778.4</v>
       </c>
       <c r="I6" t="n">
-        <v>17053.5</v>
+        <v>3757.5</v>
       </c>
       <c r="J6" t="n">
         <v>150937.7</v>
@@ -1287,7 +1287,7 @@
         <v>5724.4</v>
       </c>
       <c r="I7" t="n">
-        <v>17760.2</v>
+        <v>3575.2</v>
       </c>
       <c r="J7" t="n">
         <v>156388.5</v>

--- a/output/Data and Chart Outputs/canada_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/canada_power_capacity.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -824,7 +825,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -839,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -919,7 +918,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -948,7 +947,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -977,7 +976,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1006,7 +1005,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">

--- a/output/Data and Chart Outputs/canada_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/canada_power_capacity.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Canada installed generating capacity (StatCan, annual) (to 2024)</a:t>
             </a:r>
           </a:p>
@@ -289,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -317,7 +318,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -345,7 +346,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -373,7 +374,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>

--- a/output/Data and Chart Outputs/canada_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/canada_power_capacity.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,7 +156,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Canada installed generating capacity (StatCan, annual) (to 2024)</a:t>
+              <a:t>Canada installed generating capacity (StatCan, annual) (to 2025)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -383,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -826,6 +825,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -836,10 +836,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Canada, annual, 2019 to 2024. StatCan publishes these tables about a year after the year ends; the dashboard carries the latest year forward.</t>
-        </is>
-      </c>
-    </row>
+          <t>Canada, annual, 2019 to 2025. StatCan publishes these tables about a year after the year ends; the dashboard carries the latest year forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -919,7 +920,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -948,7 +949,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -977,7 +978,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1006,20 +1007,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
-        <v>83.0528</v>
+        <v>83.02210000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>24.108</v>
+        <v>24.336</v>
       </c>
       <c r="D5" t="n">
-        <v>17.2874</v>
+        <v>17.738</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2402</v>
+        <v>5.2881</v>
       </c>
       <c r="F5" t="n">
         <v>5.724399999999999</v>
@@ -1031,7 +1032,36 @@
         <v>3.2155</v>
       </c>
       <c r="I5" t="n">
-        <v>17.7602</v>
+        <v>16.4252</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83.03749999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24.4448</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18.3824</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.7285</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.7704</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.2155</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.3272</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,31 +1296,63 @@
         <v>45292</v>
       </c>
       <c r="B7" t="n">
-        <v>83052.8</v>
+        <v>83022.10000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>24108</v>
+        <v>24336</v>
       </c>
       <c r="D7" t="n">
-        <v>17287.4</v>
+        <v>17738</v>
       </c>
       <c r="E7" t="n">
-        <v>5240.2</v>
+        <v>5288.1</v>
       </c>
       <c r="F7" t="n">
         <v>3215.5</v>
       </c>
       <c r="G7" t="n">
-        <v>14185</v>
+        <v>12939</v>
       </c>
       <c r="H7" t="n">
         <v>5724.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3575.2</v>
+        <v>3486.2</v>
       </c>
       <c r="J7" t="n">
-        <v>156388.5</v>
+        <v>155749.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83037.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>24444.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18382.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5728.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3215.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11907</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5770.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3420.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>155906.4</v>
       </c>
     </row>
   </sheetData>
